--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104630_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104630_W20.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8795</v>
+        <v>5.6467</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0772</v>
+        <v>4.0091</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8023</v>
+        <v>1.6376</v>
       </c>
       <c r="G2" t="n">
-        <v>1.4765</v>
+        <v>1.4792</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2366</v>
+        <v>1.2378</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2399</v>
+        <v>0.2414</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.025</v>
+        <v>-0.0439</v>
       </c>
       <c r="K2" t="n">
-        <v>0.876</v>
+        <v>0.8651</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.901</v>
+        <v>-0.909</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5015</v>
+        <v>1.5231</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1409</v>
+        <v>1.1504</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6713</v>
+        <v>0.4438</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6635</v>
+        <v>0.6268</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0078</v>
+        <v>-0.183</v>
       </c>
       <c r="V2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W2" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4604</v>
+        <v>2.8597</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3263</v>
+        <v>0.595</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1341</v>
+        <v>2.2646</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3692</v>
+        <v>4.3775</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8253</v>
+        <v>3.8229</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.5546</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6562</v>
+        <v>2.6236</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5069</v>
+        <v>2.4746</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M3" t="n">
-        <v>1.713</v>
+        <v>1.7539</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3184</v>
+        <v>1.3482</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1308</v>
+        <v>-0.4676</v>
       </c>
       <c r="T3" t="n">
-        <v>0.617</v>
+        <v>-0.0678</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5138</v>
+        <v>-0.3998</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. RICHARDSON</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.7673</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1478</v>
+        <v>-2.7671</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6196</v>
+        <v>2.8439</v>
       </c>
       <c r="G4" t="n">
-        <v>2.257</v>
+        <v>-0.7746</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1167</v>
+        <v>-0.2995</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1404</v>
+        <v>-0.4751</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3923</v>
+        <v>-2.8573</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.1398</v>
+        <v>-1.3897</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5321</v>
+        <v>-1.4676</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8647</v>
+        <v>2.0826</v>
       </c>
       <c r="N4" t="n">
-        <v>1.2565</v>
+        <v>1.0901</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3918</v>
+        <v>0.9925</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7729</v>
+        <v>-0.5144</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.113</v>
+        <v>0.0902</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6599</v>
+        <v>-0.6045</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.4783</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>J. RICHARDSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8086</v>
+        <v>0.0348</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.1515</v>
+        <v>0.2425</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3429</v>
+        <v>-0.2078</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7919</v>
+        <v>2.2614</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3148</v>
+        <v>0.1286</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4771</v>
+        <v>2.1328</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.843</v>
+        <v>1.3684</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3822</v>
+        <v>-1.1484</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.4608</v>
+        <v>2.5168</v>
       </c>
       <c r="M5" t="n">
-        <v>2.0511</v>
+        <v>0.893</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0674</v>
+        <v>1.277</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9837</v>
+        <v>-0.384</v>
       </c>
       <c r="P5" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3776</v>
+        <v>-0.9778</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3085</v>
+        <v>-0.6902</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0692</v>
+        <v>-0.2876</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.4764</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1001</v>
+        <v>-1.4176</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1379</v>
+        <v>-1.4495</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0378</v>
+        <v>0.0319</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1619</v>
+        <v>1.1696</v>
       </c>
       <c r="H6" t="n">
-        <v>1.479</v>
+        <v>1.4791</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3171</v>
+        <v>-0.3095</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4068</v>
+        <v>0.3912</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3321</v>
+        <v>0.3168</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7551</v>
+        <v>0.7784</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1469</v>
+        <v>1.1623</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.039</v>
+        <v>-0.3564</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0393</v>
+        <v>-0.2442</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0784</v>
+        <v>-0.1122</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5425</v>
+        <v>-1.5479</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4498</v>
+        <v>-0.4584</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0229</v>
+        <v>-1.6219</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9777</v>
+        <v>-0.5565</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0452</v>
+        <v>-1.0654</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9658</v>
+        <v>-0.9576</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.534</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1967</v>
+        <v>-0.1852</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1000,22 +1000,22 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5108</v>
+        <v>-0.1195</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2087</v>
+        <v>0.2159</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3021</v>
+        <v>-0.3355</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3717</v>
+        <v>-1.7472</v>
       </c>
       <c r="E8" t="n">
-        <v>-6.21</v>
+        <v>-5.2107</v>
       </c>
       <c r="F8" t="n">
-        <v>3.8383</v>
+        <v>3.4635</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5516</v>
+        <v>1.5621</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1673</v>
+        <v>-1.1689</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7189</v>
+        <v>2.731</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3335</v>
+        <v>-1.3534</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.9679</v>
+        <v>-1.9865</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8851</v>
+        <v>2.9156</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8006</v>
+        <v>0.8176</v>
       </c>
       <c r="O8" t="n">
-        <v>2.0846</v>
+        <v>2.098</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4528</v>
+        <v>0.1734</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8861</v>
+        <v>0.1506</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4334</v>
+        <v>0.0228</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5254</v>
+        <v>-2.3803</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1187</v>
+        <v>-2.0642</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4066</v>
+        <v>-0.3161</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4593</v>
+        <v>-0.4494</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8139</v>
+        <v>-0.8101</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.3071</v>
+        <v>-2.3172</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.5208</v>
+        <v>-1.5276</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M9" t="n">
-        <v>1.8478</v>
+        <v>1.8678</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1409</v>
+        <v>1.1504</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.291</v>
+        <v>-0.1601</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2299</v>
+        <v>0.3017</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5208</v>
+        <v>-0.4618</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9438</v>
+        <v>-4.1961</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2482</v>
+        <v>-3.2835</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6956</v>
+        <v>-0.9126</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0556</v>
+        <v>-0.0581</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.466</v>
+        <v>0.4067</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4104</v>
+        <v>-0.4648</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7558</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.7152</v>
+        <v>-0.3242</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9594</v>
+        <v>-0.2388</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2998</v>
+        <v>0.5049</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2493</v>
+        <v>0.731</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.549</v>
+        <v>-0.226</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.2683</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6199</v>
+        <v>-1.0486</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1825</v>
+        <v>-0.602</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4374</v>
+        <v>-0.4466</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2464</v>
+        <v>-4.2939</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8201</v>
+        <v>-3.8196</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4263</v>
+        <v>-0.4743</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0774</v>
+        <v>-1.0747</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3864</v>
+        <v>-1.4703</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4638</v>
+        <v>0.3956</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5481</v>
+        <v>-0.8044</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3188</v>
+        <v>-1.7419</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2293</v>
+        <v>0.9375</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4707</v>
+        <v>-0.2703</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7052</v>
+        <v>0.2716</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2345</v>
+        <v>-0.5419</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9073</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0763</v>
+        <v>-0.9429</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1644</v>
+        <v>-0.6902</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9119</v>
+        <v>-0.2527</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.3461</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.446300000000001</v>
+        <v>-7.039000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.4084</v>
+        <v>-14.3045</v>
       </c>
       <c r="F12" t="n">
-        <v>6.9621</v>
+        <v>7.2653</v>
       </c>
       <c r="G12" t="n">
-        <v>7.4662</v>
+        <v>7.535400000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>2.747999999999999</v>
+        <v>2.797600000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7183</v>
+        <v>4.7379</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.126199999999999</v>
+        <v>-4.328399999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.3124</v>
+        <v>-4.444599999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1858999999999997</v>
+        <v>0.1161</v>
       </c>
       <c r="M12" t="n">
-        <v>11.5925</v>
+        <v>11.8638</v>
       </c>
       <c r="N12" t="n">
-        <v>7.0604</v>
+        <v>7.2419</v>
       </c>
       <c r="O12" t="n">
-        <v>4.5322</v>
+        <v>4.6219</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.9391</v>
+        <v>-7.967</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.8784</v>
+        <v>-15.9343</v>
       </c>
       <c r="R12" t="n">
-        <v>7.9392</v>
+        <v>7.9672</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.3382</v>
+        <v>-3.9701</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.3135</v>
+        <v>-0.9092</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.0247</v>
+        <v>-3.0609</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.6352</v>
+        <v>-2.6373</v>
       </c>
       <c r="W12" t="n">
-        <v>6.9098</v>
+        <v>6.8673</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.544899999999998</v>
+        <v>-9.5046</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7802</v>
+        <v>5.0965</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2351</v>
+        <v>1.4327</v>
       </c>
       <c r="F13" t="n">
-        <v>3.5451</v>
+        <v>3.6638</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0443</v>
+        <v>-0.0526</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4142</v>
+        <v>0.4109</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4585</v>
+        <v>-0.4635</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.263</v>
+        <v>-1.2887</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9218</v>
+        <v>-0.9383</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2187</v>
+        <v>1.2361</v>
       </c>
       <c r="N13" t="n">
-        <v>1.336</v>
+        <v>1.3492</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P13" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1155</v>
+        <v>0.4482</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1693</v>
+        <v>0.0692</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2849</v>
+        <v>0.379</v>
       </c>
       <c r="V13" t="n">
-        <v>2.6675</v>
+        <v>2.6522</v>
       </c>
       <c r="W13" t="n">
-        <v>2.6675</v>
+        <v>2.6522</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3716</v>
+        <v>3.6</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3241</v>
+        <v>1.0582</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0475</v>
+        <v>2.5418</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5931</v>
+        <v>1.5422</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9641</v>
+        <v>0.7961</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6291</v>
+        <v>0.746</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8462</v>
+        <v>0.0772</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0999</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7463</v>
+        <v>0.1708</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7469</v>
+        <v>1.465</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8641</v>
+        <v>0.8898</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1172</v>
+        <v>0.5752</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>2.2763</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9638</v>
+        <v>0.3262</v>
       </c>
       <c r="T14" t="n">
-        <v>1.612</v>
+        <v>0.4363</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3517</v>
+        <v>-0.11</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3055</v>
+        <v>3.2885</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8508</v>
+        <v>0.2765</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4547</v>
+        <v>3.012</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5584</v>
+        <v>-2.4488</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8068</v>
+        <v>-2.8162</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7516</v>
+        <v>0.3673</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1079</v>
+        <v>-2.5943</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0733</v>
+        <v>-2.9732</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1812</v>
+        <v>0.3789</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4505</v>
+        <v>0.1454</v>
       </c>
       <c r="N15" t="n">
-        <v>0.88</v>
+        <v>0.157</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5705</v>
+        <v>-0.0116</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2683</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2683</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0251</v>
+        <v>1.1518</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1966</v>
+        <v>0.7892</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1715</v>
+        <v>0.3627</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5463</v>
+        <v>4.3579</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5463</v>
+        <v>4.3579</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. TOMIC</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1286</v>
+        <v>2.5739</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1461</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9825</v>
+        <v>1.9786</v>
       </c>
       <c r="G16" t="n">
-        <v>0.882</v>
+        <v>1.5858</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8069</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9249000000000001</v>
+        <v>0.6317</v>
       </c>
       <c r="J16" t="n">
-        <v>0.996</v>
+        <v>0.8234</v>
       </c>
       <c r="K16" t="n">
-        <v>1.745</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.749</v>
+        <v>0.7447</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.114</v>
+        <v>0.7623</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0619</v>
+        <v>0.8754</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1759</v>
+        <v>-0.113</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8649</v>
+        <v>1.167</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9648</v>
+        <v>0.91</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9001</v>
+        <v>0.257</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8354</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.2891</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>A. TOMIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2199</v>
+        <v>2.4657</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0122</v>
+        <v>0.6394</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2321</v>
+        <v>1.8263</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9235</v>
+        <v>0.8656</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4487</v>
+        <v>1.7875</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5251</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3574</v>
+        <v>0.9638</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9626</v>
+        <v>1.7162</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6052</v>
+        <v>-0.7524</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5661</v>
+        <v>-0.0982</v>
       </c>
       <c r="N17" t="n">
-        <v>0.486</v>
+        <v>0.0713</v>
       </c>
       <c r="O17" t="n">
-        <v>0.08</v>
+        <v>-0.1695</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8378</v>
+        <v>1.2101</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3035</v>
+        <v>0.4967</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4657</v>
+        <v>0.7134</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.8454</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>0.3007</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1489</v>
+        <v>2.0505</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2974</v>
+        <v>-0.2141</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4463</v>
+        <v>2.2646</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4107</v>
+        <v>0.924</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.7917</v>
+        <v>1.453</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3811</v>
+        <v>-0.529</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.5318</v>
+        <v>0.3325</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.9314</v>
+        <v>0.9513</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3997</v>
+        <v>-0.6188</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1211</v>
+        <v>0.5916</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1397</v>
+        <v>0.5018</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0186</v>
+        <v>0.0898</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.038</v>
+        <v>-0.0117</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.868</v>
+        <v>-0.4767</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.17</v>
+        <v>0.465</v>
       </c>
       <c r="V18" t="n">
-        <v>4.3707</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4.3707</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.791</v>
+        <v>-0.882</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9214</v>
+        <v>-1.5503</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1304</v>
+        <v>0.6684</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.2348</v>
+        <v>-2.4268</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.078</v>
+        <v>0.2413</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1568</v>
+        <v>-2.6681</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.0496</v>
+        <v>-2.3141</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.1859</v>
+        <v>-0.1314</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8637</v>
+        <v>-2.1827</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1852</v>
+        <v>-0.1127</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1079</v>
+        <v>0.3727</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2931</v>
+        <v>-0.4854</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>3.0828</v>
+        <v>1.267</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4892</v>
+        <v>0.7638</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5937</v>
+        <v>0.5032</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>-0.8603</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8055</v>
+        <v>-1.8422</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4135</v>
+        <v>-0.7179</v>
       </c>
       <c r="F20" t="n">
-        <v>0.608</v>
+        <v>-1.1243</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4205</v>
+        <v>-0.5088</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2424</v>
+        <v>-0.1095</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.6629</v>
+        <v>-0.3993</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.2906</v>
+        <v>-0.267</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1181</v>
+        <v>0.1207</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.1725</v>
+        <v>-0.3877</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1299</v>
+        <v>-0.2417</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3605</v>
+        <v>-0.2301</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4904</v>
+        <v>-0.0116</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3486</v>
+        <v>-0.4716</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8771</v>
+        <v>-0.2232</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4715</v>
+        <v>-0.2483</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7209</v>
+        <v>-2.1437</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1477</v>
+        <v>-2.636</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4269</v>
+        <v>0.4922</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3507</v>
+        <v>-1.3389</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8413</v>
+        <v>-1.8383</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4905</v>
+        <v>0.4994</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.1486</v>
+        <v>-2.1593</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.1859</v>
+        <v>-2.1966</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.8204</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3369</v>
+        <v>-0.1024</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2692</v>
+        <v>-0.2003</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0677</v>
+        <v>0.098</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5085</v>
+        <v>-2.474</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1798</v>
+        <v>-3.7079</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3287</v>
+        <v>1.2338</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5127</v>
+        <v>-3.2228</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1155</v>
+        <v>-2.0684</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3972</v>
+        <v>-1.1543</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2574</v>
+        <v>-3.0683</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1212</v>
+        <v>-2.1966</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3786</v>
+        <v>-0.8718</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2554</v>
+        <v>-0.1544</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2368</v>
+        <v>0.1281</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0186</v>
+        <v>-0.2826</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1299</v>
+        <v>1.383</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6956</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4343</v>
+        <v>0.6567</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6825</v>
+        <v>-2.5103</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5462</v>
+        <v>-2.4412</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1364</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4495</v>
+        <v>-2.4543</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6045</v>
+        <v>-1.6082</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.845</v>
+        <v>-0.8462</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.3591</v>
+        <v>-2.3689</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.0854</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2248,19 +2248,19 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3938</v>
+        <v>-0.2137</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3478</v>
+        <v>-0.2301</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.046</v>
+        <v>0.0163</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>8.446299999999997</v>
+        <v>9.222899999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.9621</v>
+        <v>-7.2653</v>
       </c>
       <c r="F24" t="n">
-        <v>15.4084</v>
+        <v>16.4881</v>
       </c>
       <c r="G24" t="n">
-        <v>-7.466200000000001</v>
+        <v>-7.535399999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.7479</v>
+        <v>-2.7977</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.7181</v>
+        <v>-4.7379</v>
       </c>
       <c r="J24" t="n">
-        <v>-11.5926</v>
+        <v>-11.8637</v>
       </c>
       <c r="K24" t="n">
-        <v>-7.0604</v>
+        <v>-7.2422</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.5322</v>
+        <v>-4.6219</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1263</v>
+        <v>4.328400000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3121</v>
+        <v>4.444599999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1859000000000001</v>
+        <v>-0.1159999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>7.939100000000001</v>
+        <v>7.9671</v>
       </c>
       <c r="Q24" t="n">
-        <v>-7.9391</v>
+        <v>-7.9671</v>
       </c>
       <c r="R24" t="n">
-        <v>15.8784</v>
+        <v>15.9343</v>
       </c>
       <c r="S24" t="n">
-        <v>5.3381</v>
+        <v>6.153899999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>3.0247</v>
+        <v>3.061199999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>2.3135</v>
+        <v>3.093</v>
       </c>
       <c r="V24" t="n">
-        <v>2.635</v>
+        <v>2.6373</v>
       </c>
       <c r="W24" t="n">
-        <v>9.544900000000002</v>
+        <v>9.5046</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.909899999999999</v>
+        <v>-6.8674</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104630_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104630_W20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-9.5046</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.3007</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104630_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-6.8674</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
